--- a/data/trans_orig/P45C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226680</t>
+          <t>227101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249607</t>
+          <t>248426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>209196</t>
+          <t>210134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>233387</t>
+          <t>233287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>445770</t>
+          <t>443514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>475447</t>
+          <t>475671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46330</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51642</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88078</t>
+          <t>90334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354644</t>
+          <t>355384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393152</t>
+          <t>392750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>383724</t>
+          <t>382851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>419793</t>
+          <t>419195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>750746</t>
+          <t>748442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>804042</t>
+          <t>802904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86046</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123361</t>
+          <t>122096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70513</t>
+          <t>71605</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>105528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>166596</t>
+          <t>166985</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>217300</t>
+          <t>216708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>23126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>41703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>266094</t>
+          <t>266486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289027</t>
+          <t>289469</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>284569</t>
+          <t>283984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>306924</t>
+          <t>306346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>560135</t>
+          <t>557838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>591454</t>
+          <t>590896</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61837</t>
+          <t>62372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93125</t>
+          <t>95732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>259596</t>
+          <t>260353</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>291541</t>
+          <t>291554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>310777</t>
+          <t>311559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335782</t>
+          <t>336225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>580193</t>
+          <t>580537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>620768</t>
+          <t>621598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56808</t>
+          <t>57682</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>33320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58596</t>
+          <t>57327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97689</t>
+          <t>97945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136026</t>
+          <t>136731</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183969</t>
+          <t>183396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>197243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187278</t>
+          <t>185689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>200100</t>
+          <t>199744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>376243</t>
+          <t>376045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394474</t>
+          <t>394428</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34435</t>
+          <t>34366</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>186848</t>
+          <t>186628</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216259</t>
+          <t>216373</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>220060</t>
+          <t>218932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>243046</t>
+          <t>243648</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>411558</t>
+          <t>414551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>452309</t>
+          <t>452648</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53514</t>
+          <t>52957</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81712</t>
+          <t>82354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93615</t>
+          <t>91957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133449</t>
+          <t>131281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>515781</t>
+          <t>518799</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>550604</t>
+          <t>551845</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>558394</t>
+          <t>558847</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>588360</t>
+          <t>588795</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1085528</t>
+          <t>1084100</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1132982</t>
+          <t>1129486</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50713</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>81419</t>
+          <t>81383</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33031</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>58423</t>
+          <t>58852</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>89623</t>
+          <t>93265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>132057</t>
+          <t>131802</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26075</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>27453</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>640033</t>
+          <t>640635</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>672296</t>
+          <t>673680</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>686091</t>
+          <t>683056</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>718412</t>
+          <t>718807</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1335630</t>
+          <t>1337458</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1381631</t>
+          <t>1383824</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>51788</t>
+          <t>50774</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>82832</t>
+          <t>81887</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>40900</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>70030</t>
+          <t>69987</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>100440</t>
+          <t>100357</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>140870</t>
+          <t>142274</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>21511</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>22211</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45233</t>
+          <t>44644</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>418862</t>
+          <t>417405</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>500495</t>
+          <t>501386</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>327905</t>
+          <t>328046</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>398378</t>
+          <t>398532</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>765457</t>
+          <t>771904</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>876218</t>
+          <t>871480</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>41915</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>72746</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>73097</t>
+          <t>72232</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>92113</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>133070</t>
+          <t>136039</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>227025</t>
+          <t>224441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255698</t>
+          <t>253441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231109</t>
+          <t>232541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>256027</t>
+          <t>257167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>466310</t>
+          <t>467938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>505243</t>
+          <t>504140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>33557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56708</t>
+          <t>58769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>47343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99433</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422493</t>
+          <t>421645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>451450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448156</t>
+          <t>448388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476009</t>
+          <t>475646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877263</t>
+          <t>878132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919499</t>
+          <t>918383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69635</t>
+          <t>71400</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63755</t>
+          <t>63240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>85222</t>
+          <t>87200</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126294</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11775</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208582</t>
+          <t>208113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>240382</t>
+          <t>241323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>267565</t>
+          <t>266111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>296314</t>
+          <t>294669</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>482473</t>
+          <t>483957</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>528903</t>
+          <t>530632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81414</t>
+          <t>81210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113350</t>
+          <t>113234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58923</t>
+          <t>60034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122240</t>
+          <t>120828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168101</t>
+          <t>165416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>308204</t>
+          <t>308699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>334156</t>
+          <t>335335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>339433</t>
+          <t>339107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>363345</t>
+          <t>362706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>654339</t>
+          <t>655888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>690487</t>
+          <t>692319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20167</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>32005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61206</t>
+          <t>59629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,47 +6682,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>16037</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>25613</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>16037</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>9255</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25246</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>44775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178606</t>
+          <t>179337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197492</t>
+          <t>197393</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184476</t>
+          <t>184867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202753</t>
+          <t>203331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396702</t>
+          <t>395433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>33281</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32018</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32370</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>166296</t>
+          <t>165440</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>198829</t>
+          <t>196286</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>201083</t>
+          <t>198736</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>229369</t>
+          <t>228435</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>372474</t>
+          <t>375570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>416657</t>
+          <t>416239</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70160</t>
+          <t>71960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101658</t>
+          <t>102166</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>46957</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74018</t>
+          <t>75562</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126876</t>
+          <t>127224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170029</t>
+          <t>168947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>466668</t>
+          <t>466203</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>511138</t>
+          <t>512743</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>516508</t>
+          <t>518135</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>561725</t>
+          <t>562538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>998884</t>
+          <t>1000095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1063044</t>
+          <t>1062012</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>143309</t>
+          <t>141496</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187332</t>
+          <t>187131</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116899</t>
+          <t>117809</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>162264</t>
+          <t>161884</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271172</t>
+          <t>270821</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>333841</t>
+          <t>332547</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19909</t>
+          <t>18151</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>696105</t>
+          <t>694425</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>724531</t>
+          <t>726225</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>739372</t>
+          <t>740229</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>767577</t>
+          <t>769218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1445267</t>
+          <t>1442778</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1487477</t>
+          <t>1484599</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>42849</t>
+          <t>42531</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>70996</t>
+          <t>73634</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40655</t>
+          <t>38740</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>68382</t>
+          <t>67861</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>90166</t>
+          <t>91153</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>129952</t>
+          <t>131631</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16348</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2757294</t>
+          <t>2755487</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2847854</t>
+          <t>2847553</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3008035</t>
+          <t>3006014</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3091474</t>
+          <t>3085325</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5786272</t>
+          <t>5790644</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5910210</t>
+          <t>5910279</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>508366</t>
+          <t>507133</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>598366</t>
+          <t>598562</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>378936</t>
+          <t>382536</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>459093</t>
+          <t>458186</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>913835</t>
+          <t>910374</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1027388</t>
+          <t>1031273</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>59707</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>72597</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>82768</t>
+          <t>79250</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>120888</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>220590</t>
+          <t>220130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>250007</t>
+          <t>249192</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>232111</t>
+          <t>233579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>256728</t>
+          <t>256287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>460282</t>
+          <t>464472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>499136</t>
+          <t>501608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62012</t>
+          <t>61461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>25673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64142</t>
+          <t>66345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100105</t>
+          <t>99963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418984</t>
+          <t>417509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448572</t>
+          <t>448053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427427</t>
+          <t>425968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459320</t>
+          <t>458711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>856302</t>
+          <t>854790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>899220</t>
+          <t>901571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47691</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55572</t>
+          <t>56932</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87135</t>
+          <t>88351</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112509</t>
+          <t>110014</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>154725</t>
+          <t>154474</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275117</t>
+          <t>275241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>296029</t>
+          <t>295282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>279118</t>
+          <t>279603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>302623</t>
+          <t>302583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>561748</t>
+          <t>561061</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>592280</t>
+          <t>591926</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55945</t>
+          <t>55929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85916</t>
+          <t>85832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>302019</t>
+          <t>302836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>331061</t>
+          <t>329916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>327748</t>
+          <t>327399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>353244</t>
+          <t>353641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>638503</t>
+          <t>637804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>678544</t>
+          <t>675739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35202</t>
+          <t>35012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>61455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23430</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47451</t>
+          <t>47405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62913</t>
+          <t>64737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99352</t>
+          <t>99648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196430</t>
+          <t>197016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214148</t>
+          <t>214387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>414479</t>
+          <t>413872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>426213</t>
+          <t>426180</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>250154</t>
+          <t>250015</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>260088</t>
+          <t>260109</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>253071</t>
+          <t>253814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>266155</t>
+          <t>266217</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>507404</t>
+          <t>506733</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>523576</t>
+          <t>523553</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>530750</t>
+          <t>529357</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>568422</t>
+          <t>568521</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547291</t>
+          <t>548140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>585446</t>
+          <t>587031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1090974</t>
+          <t>1091447</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1147329</t>
+          <t>1145435</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67151</t>
+          <t>68819</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>103181</t>
+          <t>106093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87460</t>
+          <t>85722</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125400</t>
+          <t>123354</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>163048</t>
+          <t>164263</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>216426</t>
+          <t>217933</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>600956</t>
+          <t>599544</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>645365</t>
+          <t>644427</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>646403</t>
+          <t>646119</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>690853</t>
+          <t>690989</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1261830</t>
+          <t>1264485</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1324414</t>
+          <t>1328589</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>120397</t>
+          <t>123131</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>166010</t>
+          <t>168098</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>126699</t>
+          <t>126365</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>169486</t>
+          <t>169211</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>257803</t>
+          <t>257156</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>320859</t>
+          <t>321562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2868558</t>
+          <t>2872186</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2953974</t>
+          <t>2953273</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3001178</t>
+          <t>2997251</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3082182</t>
+          <t>3080889</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5896891</t>
+          <t>5892567</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6007079</t>
+          <t>6007281</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>381603</t>
+          <t>382515</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>461787</t>
+          <t>461252</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>398811</t>
+          <t>400362</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>478903</t>
+          <t>478364</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>807294</t>
+          <t>807743</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>912590</t>
+          <t>914266</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>43526</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>53496</t>
+          <t>52384</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>55294</t>
+          <t>53130</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>91240</t>
+          <t>88717</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -13783,27 +13783,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>289122</t>
+          <t>315568</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>287048</t>
+          <t>313535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -13818,27 +13818,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>600564</t>
+          <t>634413</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>598144</t>
+          <t>632453</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>493</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -13941,12 +13941,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14204,32 +14204,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>426284</t>
+          <t>438525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401306</t>
+          <t>414668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447703</t>
+          <t>457429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14239,32 +14239,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>433095</t>
+          <t>461076</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417632</t>
+          <t>443866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449252</t>
+          <t>476270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,32 +14274,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>859379</t>
+          <t>899601</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829411</t>
+          <t>870963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886492</t>
+          <t>925398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -14317,32 +14317,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69283</t>
+          <t>68405</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50018</t>
+          <t>50120</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92568</t>
+          <t>88642</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55689</t>
+          <t>59216</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44267</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71244</t>
+          <t>75465</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>124972</t>
+          <t>127621</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101717</t>
+          <t>105159</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153807</t>
+          <t>151521</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -14430,32 +14430,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35168</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>35810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47003</t>
+          <t>47955</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34731</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64959</t>
+          <t>64537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>516978</t>
+          <t>529291</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516978</t>
+          <t>529291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516978</t>
+          <t>529291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514376</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514376</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514376</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1075177</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1075177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1075177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>295692</t>
+          <t>293779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285450</t>
+          <t>283090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>302260</t>
+          <t>301812</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>322335</t>
+          <t>329687</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310029</t>
+          <t>318002</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>330631</t>
+          <t>338042</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>618027</t>
+          <t>623466</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>603234</t>
+          <t>608247</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>631032</t>
+          <t>634459</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,32 +14843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>44696</t>
+          <t>46032</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>61641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>315451</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315451</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315451</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>664579</t>
+          <t>671765</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>664579</t>
+          <t>671765</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>664579</t>
+          <t>671765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15116,32 +15116,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>264562</t>
+          <t>315866</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>236538</t>
+          <t>293857</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>279108</t>
+          <t>333619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>433147</t>
+          <t>374943</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>418525</t>
+          <t>361537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>450414</t>
+          <t>386177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,32 +15186,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>697709</t>
+          <t>690810</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>666038</t>
+          <t>661781</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>722940</t>
+          <t>711967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -15229,32 +15229,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68371</t>
+          <t>72208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41300</t>
+          <t>44990</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55970</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>83385</t>
+          <t>94906</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>73322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113366</t>
+          <t>121802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -15342,32 +15342,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>437</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>785931</t>
+          <t>792616</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>785931</t>
+          <t>792616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>785931</t>
+          <t>792616</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15572,32 +15572,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>168904</t>
+          <t>193374</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162117</t>
+          <t>185332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173098</t>
+          <t>198203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15607,32 +15607,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>199660</t>
+          <t>218386</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191672</t>
+          <t>210634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203593</t>
+          <t>222124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,32 +15642,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>368564</t>
+          <t>411760</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>359536</t>
+          <t>401504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>374401</t>
+          <t>418749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>208558</t>
+          <t>212118</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194784</t>
+          <t>198486</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221242</t>
+          <t>223406</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>181702</t>
+          <t>186668</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>169578</t>
+          <t>172452</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>192695</t>
+          <t>197499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>390260</t>
+          <t>398786</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>371689</t>
+          <t>381493</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>408098</t>
+          <t>413716</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -16141,32 +16141,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>54205</t>
+          <t>51895</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>41422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67974</t>
+          <t>65643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>70126</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58253</t>
+          <t>59606</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80892</t>
+          <t>83688</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>122916</t>
+          <t>122021</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106507</t>
+          <t>107415</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140747</t>
+          <t>137926</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,22 +16324,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20472</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>268837</t>
+          <t>269907</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>268837</t>
+          <t>269907</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>268837</t>
+          <t>269907</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>525893</t>
+          <t>533658</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>525893</t>
+          <t>533658</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>525893</t>
+          <t>533658</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16484,32 +16484,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>537817</t>
+          <t>613484</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>514890</t>
+          <t>587474</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>557711</t>
+          <t>635336</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>764048</t>
+          <t>666127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>726440</t>
+          <t>642113</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>807855</t>
+          <t>684748</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1301865</t>
+          <t>1279611</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1261676</t>
+          <t>1245905</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1364354</t>
+          <t>1307101</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -16597,32 +16597,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>70263</t>
+          <t>88228</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52934</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>112526</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>72164</t>
+          <t>87722</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>70777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104615</t>
+          <t>110078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>142427</t>
+          <t>175951</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>89283</t>
+          <t>149838</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>179349</t>
+          <t>207353</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -16710,32 +16710,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>27835</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22967</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>32506</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>43213</t>
+          <t>46854</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>622147</t>
+          <t>717449</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>622147</t>
+          <t>717449</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>622147</t>
+          <t>717449</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>849103</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>849103</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>849103</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1471249</t>
+          <t>1488068</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1471249</t>
+          <t>1488068</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1471249</t>
+          <t>1488068</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16940,32 +16940,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>707254</t>
+          <t>541076</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>615734</t>
+          <t>510104</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>820340</t>
+          <t>566124</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16975,32 +16975,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>585569</t>
+          <t>680814</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>566352</t>
+          <t>659345</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>602419</t>
+          <t>699721</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17010,32 +17010,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1292824</t>
+          <t>1221890</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1219215</t>
+          <t>1186337</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1426536</t>
+          <t>1257681</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -17053,32 +17053,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>245653</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>101509</t>
+          <t>221354</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>298230</t>
+          <t>278639</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>126819</t>
+          <t>144551</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110319</t>
+          <t>125055</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>145410</t>
+          <t>165866</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>338115</t>
+          <t>390204</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>206936</t>
+          <t>355855</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>408591</t>
+          <t>426858</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -17166,32 +17166,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17201,22 +17201,22 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>715832</t>
+          <t>829176</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>715832</t>
+          <t>829176</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>715832</t>
+          <t>829176</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1644553</t>
+          <t>1627248</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1644553</t>
+          <t>1627248</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1644553</t>
+          <t>1627248</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2920513</t>
+          <t>2927068</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2850514</t>
+          <t>2868717</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3036571</t>
+          <t>2978530</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3208677</t>
+          <t>3233269</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3160073</t>
+          <t>3191955</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3291561</t>
+          <t>3270933</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>6129190</t>
+          <t>6160337</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6040436</t>
+          <t>6089655</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6261619</t>
+          <t>6221444</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>476728</t>
+          <t>537993</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>368642</t>
+          <t>485319</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>540816</t>
+          <t>593230</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>398747</t>
+          <t>439962</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>319593</t>
+          <t>404162</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>442190</t>
+          <t>478418</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>875475</t>
+          <t>977955</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>919849</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>956689</t>
+          <t>1046423</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>39776</t>
+          <t>44235</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>77503</t>
+          <t>80260</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>67394</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>84783</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>141205</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
